--- a/WorkBot/refactor-experimental/data/orders/Copper Horse Coffee/Copper Horse Coffee_Easthill_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Copper Horse Coffee/Copper Horse Coffee_Easthill_20251114.xlsx
@@ -450,20 +450,14 @@
           <t>Copper Horse - Warhorse 5lb</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>55.99</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>111.98</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>55.99</v>
+      </c>
+      <c r="E2" t="n">
+        <v>111.98</v>
       </c>
     </row>
   </sheetData>
